--- a/AAII_Financials/Quarterly/AGRPY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AGRPY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="92">
   <si>
     <t>AGRPY</t>
   </si>
@@ -656,77 +656,83 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -772,8 +778,14 @@
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -819,8 +831,14 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -866,8 +884,14 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -885,8 +909,10 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -932,8 +958,14 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -979,8 +1011,14 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1026,8 +1064,14 @@
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1073,8 +1117,14 @@
       <c r="Q15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1089,8 +1139,10 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1136,8 +1188,14 @@
       <c r="Q17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1183,8 +1241,14 @@
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1202,8 +1266,10 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1249,8 +1315,14 @@
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1296,8 +1368,14 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1343,8 +1421,14 @@
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1390,8 +1474,14 @@
       <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1437,8 +1527,14 @@
       <c r="Q24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1484,8 +1580,14 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1531,8 +1633,14 @@
       <c r="Q26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1578,8 +1686,14 @@
       <c r="Q27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1625,8 +1739,14 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1672,8 +1792,14 @@
       <c r="Q29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1719,8 +1845,14 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1766,8 +1898,14 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1813,8 +1951,14 @@
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1860,8 +2004,14 @@
       <c r="Q33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1907,8 +2057,14 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1954,60 +2110,72 @@
       <c r="Q35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2025,8 +2193,10 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2044,431 +2214,487 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2882600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2769500</v>
+      </c>
+      <c r="F41" s="3">
         <v>3234400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>3100300</v>
       </c>
-      <c r="F41" s="3">
-        <v>608400</v>
-      </c>
-      <c r="G41" s="3">
-        <v>588000</v>
-      </c>
       <c r="H41" s="3">
+        <v>910500</v>
+      </c>
+      <c r="I41" s="3">
+        <v>879900</v>
+      </c>
+      <c r="J41" s="3">
         <v>2452500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>2683700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>555700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>536900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1182400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1146300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>683500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>726700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>797100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>752100</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>16757000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>16099400</v>
+      </c>
+      <c r="F42" s="3">
         <v>17384900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>16664100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>14311900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>13831200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>12193600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>13343100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>11757200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>11360800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>14054900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>13626200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>11733600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>12475600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>15052900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>14204400</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1173200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1127100</v>
+      </c>
+      <c r="F43" s="3">
         <v>2295500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>2200300</v>
       </c>
-      <c r="F43" s="3">
-        <v>92700</v>
-      </c>
-      <c r="G43" s="3">
-        <v>89600</v>
-      </c>
       <c r="H43" s="3">
+        <v>1001800</v>
+      </c>
+      <c r="I43" s="3">
+        <v>968200</v>
+      </c>
+      <c r="J43" s="3">
         <v>1868700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>2044800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>78300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>75600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>2053800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1991200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>33900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>36100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>931100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>878600</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3">
         <v>10400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>10000</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3">
         <v>3800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>4200</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L44" s="3">
+      <c r="L44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N44" s="3">
         <v>10300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>10000</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P44" s="3">
+      <c r="P44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R44" s="3">
         <v>15200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>327700</v>
+      </c>
+      <c r="E45" s="3">
+        <v>314900</v>
+      </c>
+      <c r="F45" s="3">
         <v>783100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>750600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>264700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>255800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>361100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>395100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>211800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>204700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>284100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>275500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>582700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>619600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>367000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>346300</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>27868600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>26774900</v>
+      </c>
+      <c r="F46" s="3">
         <v>30381500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>29121800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>20461900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>19774600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>21783300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>23836900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>17046400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>16471800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>20174900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>19559600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>16958300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>18030700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>20418700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>19267700</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>17456700</v>
+      </c>
+      <c r="E47" s="3">
+        <v>16771700</v>
+      </c>
+      <c r="F47" s="3">
         <v>17600900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>16871100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>16706300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>16145200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>15475500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>16934400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>14579700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>14088300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>13922300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>13497700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>13435100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>14284700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>13959800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>13172900</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1029100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>988700</v>
+      </c>
+      <c r="F48" s="3">
         <v>969700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>929500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>889000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>859200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>860600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>941800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>856500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>827600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>875600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>848900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>824300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>876500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>901400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>850600</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>868600</v>
+      </c>
+      <c r="E49" s="3">
+        <v>834500</v>
+      </c>
+      <c r="F49" s="3">
         <v>873000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>836800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>900100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>869800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>847900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>927800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>821100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>793500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>789500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>765500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>707900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>752700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>758800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>716100</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2514,8 +2740,14 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2561,55 +2793,67 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2160600</v>
+      </c>
+      <c r="E52" s="3">
+        <v>2075800</v>
+      </c>
+      <c r="F52" s="3">
         <v>89100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>85400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>2797900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>2703900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>90700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>99300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1737700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1679100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>99900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>96900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>2036600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>2165400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>111600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>105300</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2655,55 +2899,67 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>139191100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>133728600</v>
+      </c>
+      <c r="F54" s="3">
         <v>135257100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>129649000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>121630700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>117545600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>109560300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>119888900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>107003200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>103396400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>102499800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>99373600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>100785200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>107158200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>105410300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>99468300</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2721,8 +2977,10 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2740,290 +2998,328 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>92460500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>88831900</v>
+      </c>
+      <c r="F57" s="3">
         <v>103384100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>99097500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>88880100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>85895000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>85245200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>93281500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>71865400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>69443000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>68751900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>66654900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>70279300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>74723300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>67859500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>64034300</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>13838500</v>
+      </c>
+      <c r="E58" s="3">
+        <v>13295400</v>
+      </c>
+      <c r="F58" s="3">
         <v>13427800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>12871000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>2984300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>2884100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>8850600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>9685000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>4957800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>4790700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>12660000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>12273900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>3352800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>3564800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>16757700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>15813100</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>303800</v>
+      </c>
+      <c r="E59" s="3">
+        <v>291800</v>
+      </c>
+      <c r="F59" s="3">
         <v>1587500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1521600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1139600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1101400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>995200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1089100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>3353600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>3240600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>947200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>918300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1080100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1148400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>3301600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>3115500</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>106602800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>102419200</v>
+      </c>
+      <c r="F60" s="3">
         <v>118637800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>113718800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>93004000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>89880400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>95302900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>104287400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>80176800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>77474300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>82555800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>80037800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>74712200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>79436500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>88134900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>83166800</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>15110400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>14517400</v>
+      </c>
+      <c r="F61" s="3">
         <v>976100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>935600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>12079100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>11673400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1078200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1179800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>12901200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>12466300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>7228200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>7007700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>12408400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>13193000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>5744800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>5420900</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5521800</v>
+      </c>
+      <c r="E62" s="3">
+        <v>5305100</v>
+      </c>
+      <c r="F62" s="3">
         <v>4009800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>3843500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>5962500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>5762200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>3391300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>3711000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>4519100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>4366800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>3667200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>3555300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>5158200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>5484400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>2464000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>2325100</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3069,8 +3365,14 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3116,8 +3418,14 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3163,55 +3471,67 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>127247600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>122253800</v>
+      </c>
+      <c r="F66" s="3">
         <v>123696600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>118567900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>111060400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>107330300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>99853800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>109267300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>97616400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>94326000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>93512200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>90660100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>92290400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>98126200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>96402900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>90968700</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3229,8 +3549,10 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3276,8 +3598,14 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3323,8 +3651,14 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3370,8 +3704,14 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3417,55 +3757,67 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>9468700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>9097100</v>
+      </c>
+      <c r="F72" s="3">
         <v>9085400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>8708700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>8213100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>7937300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>7455900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>8158800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>7411400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>7161600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>7175300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>6956500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>6753000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>7180000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>7236300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>6828400</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3511,8 +3863,14 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3558,8 +3916,14 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3605,55 +3969,67 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11408400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>10960700</v>
+      </c>
+      <c r="F76" s="3">
         <v>11022900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>10565900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>9831800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>9501600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>8995300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>9843400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>8713800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>8420100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>8356200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>8101400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>7891900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>8390900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>8354900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>7884000</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3699,60 +4075,72 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3798,8 +4186,14 @@
       <c r="Q81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3817,55 +4211,63 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>44600</v>
+      </c>
+      <c r="E83" s="3">
+        <v>43100</v>
+      </c>
+      <c r="F83" s="3">
         <v>4600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>5000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>80800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>78100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>8300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>8000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>41600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>44200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>96100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>90700</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R83" s="3">
         <v>113000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>120300</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3911,8 +4313,14 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3958,8 +4366,14 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4005,8 +4419,14 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4052,8 +4472,14 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4099,55 +4525,67 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1822600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-1751000</v>
+      </c>
+      <c r="F89" s="3">
         <v>-153200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-146800</v>
       </c>
-      <c r="F89" s="3">
-        <v>-2373200</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-2293500</v>
-      </c>
       <c r="H89" s="3">
+        <v>-2790300</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-2696600</v>
+      </c>
+      <c r="J89" s="3">
         <v>-1507100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1649100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-914000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-883200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-2599500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-2520200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>967500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>1028700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-1656500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-1563200</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4165,55 +4603,63 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-74400</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-71500</v>
+      </c>
+      <c r="F91" s="3">
         <v>-62700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-60100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-35000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-33800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-74300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-81300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-41500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-40100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-69500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-67400</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P91" s="3">
+      <c r="P91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R91" s="3">
         <v>-40900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-38600</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4259,8 +4705,14 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4306,55 +4758,67 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-93600</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-89900</v>
+      </c>
+      <c r="F94" s="3">
         <v>-109100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-104600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-10700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-10300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>11400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>12400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-79200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-76600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-113400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-109900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-58700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-62400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-98100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-92600</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4372,55 +4836,63 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>196700</v>
+        <v>230400</v>
       </c>
       <c r="E96" s="3">
-        <v>188500</v>
+        <v>221400</v>
       </c>
       <c r="F96" s="3">
-        <v>181500</v>
+        <v>212200</v>
       </c>
       <c r="G96" s="3">
-        <v>175400</v>
+        <v>203400</v>
       </c>
       <c r="H96" s="3">
-        <v>127100</v>
+        <v>196500</v>
       </c>
       <c r="I96" s="3">
+        <v>189900</v>
+      </c>
+      <c r="J96" s="3">
+        <v>142800</v>
+      </c>
+      <c r="K96" s="3">
         <v>139100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>179900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>173800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>154800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>150100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>143400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>152500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>142000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>134000</v>
       </c>
     </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4466,8 +4938,14 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4513,8 +4991,14 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4560,145 +5044,169 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1725900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>1658200</v>
+      </c>
+      <c r="F100" s="3">
         <v>1477200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>1416000</v>
       </c>
-      <c r="F100" s="3">
-        <v>1997700</v>
-      </c>
-      <c r="G100" s="3">
-        <v>1930600</v>
-      </c>
       <c r="H100" s="3">
+        <v>2414800</v>
+      </c>
+      <c r="I100" s="3">
+        <v>2333700</v>
+      </c>
+      <c r="J100" s="3">
         <v>2371300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>2594900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>1400600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>1353400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>2414400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>2340800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-215000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-228600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>1740700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>1642600</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F101" s="3">
         <v>-7000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-7600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-6200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-6000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>116000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>112500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-131000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-139300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-1900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-1800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>37800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>42300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>26400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>28100</v>
       </c>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-195700</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-188000</v>
+      </c>
+      <c r="F102" s="3">
         <v>1207900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>1157800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-388200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-375200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>868600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>950500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>401200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>387700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-182500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-176900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>562800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>598400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-15900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-15000</v>
       </c>
     </row>
